--- a/tabelas/FT_QTDE_EMBARQUE.xlsx
+++ b/tabelas/FT_QTDE_EMBARQUE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3f4ef99f068508f/STANG/5.MotorCalculo/MotorTransporteV2/tabelas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99477d7318b1e097/14. Gisele^0Jardel/Atuá Estratégia ^0 Análises/8. Projetos/STANG/5.MotorCalculo/01_RC_Ambiental/MotorTransporteV5/tabelas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="8_{AAF8E727-9187-4C2C-9486-D0972F4C09AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{931650DC-D29C-40E5-BF5B-84D72B0C7352}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{AAF8E727-9187-4C2C-9486-D0972F4C09AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E29657-12C2-4C94-995A-4CA3E893AB3C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77FAD20C-44E5-4827-8893-D4E5A201625A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="FT_QTDEEMBARQUE" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FT_QTDEEMBARQUE!$D$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FT_QTDEEMBARQUE!$F$1:$U$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
   <si>
     <t>NR_TARIFA</t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>De 401 a 500</t>
+  </si>
+  <si>
+    <t>CD_CARGA</t>
+  </si>
+  <si>
+    <t>DS_CARGA</t>
+  </si>
+  <si>
+    <t>PERIGOSO</t>
+  </si>
+  <si>
+    <t>COMUM</t>
   </si>
 </sst>
 </file>
@@ -563,104 +575,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B6CFE4-61AD-40DD-B0AE-A336CB719A94}">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="17" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.88671875" style="2"/>
+    <col min="2" max="3" width="13.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" style="2" customWidth="1"/>
+    <col min="9" max="19" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="U1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="8">
+      <c r="F2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="8">
+      <c r="G2" s="8">
         <v>50</v>
       </c>
-      <c r="F2" s="5">
+      <c r="H2" s="5">
         <v>1.0345569999999999</v>
       </c>
-      <c r="G2" s="5">
-        <v>1</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
       <c r="I2" s="5">
         <v>1</v>
       </c>
@@ -674,10 +694,10 @@
         <v>1</v>
       </c>
       <c r="M2" s="5">
-        <v>0.85519999999999996</v>
+        <v>1</v>
       </c>
       <c r="N2" s="5">
-        <v>0.85519999999999996</v>
+        <v>1</v>
       </c>
       <c r="O2" s="5">
         <v>0.85519999999999996</v>
@@ -688,38 +708,44 @@
       <c r="Q2" s="5">
         <v>0.85519999999999996</v>
       </c>
-      <c r="R2" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S2" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R2" s="5">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="T2" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="8">
+      <c r="F3" s="8">
         <v>51</v>
       </c>
-      <c r="E3" s="8">
+      <c r="G3" s="8">
         <v>100</v>
       </c>
-      <c r="F3" s="5">
+      <c r="H3" s="5">
         <v>1.0623499999999999</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
       <c r="I3" s="5">
         <v>1</v>
       </c>
@@ -733,10 +759,10 @@
         <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0.86439999999999995</v>
+        <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>0.86439999999999995</v>
+        <v>1</v>
       </c>
       <c r="O3" s="5">
         <v>0.86439999999999995</v>
@@ -747,38 +773,44 @@
       <c r="Q3" s="5">
         <v>0.86439999999999995</v>
       </c>
-      <c r="R3" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S3" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R3" s="5">
+        <v>0.86439999999999995</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0.86439999999999995</v>
+      </c>
+      <c r="T3" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8">
+      <c r="F4" s="8">
         <v>101</v>
       </c>
-      <c r="E4" s="8">
+      <c r="G4" s="8">
         <v>200</v>
       </c>
-      <c r="F4" s="5">
+      <c r="H4" s="5">
         <v>1.0869880000000001</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
@@ -792,10 +824,10 @@
         <v>1</v>
       </c>
       <c r="M4" s="5">
-        <v>0.88260000000000005</v>
+        <v>1</v>
       </c>
       <c r="N4" s="5">
-        <v>0.88260000000000005</v>
+        <v>1</v>
       </c>
       <c r="O4" s="5">
         <v>0.88260000000000005</v>
@@ -806,38 +838,44 @@
       <c r="Q4" s="5">
         <v>0.88260000000000005</v>
       </c>
-      <c r="R4" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S4" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R4" s="5">
+        <v>0.88260000000000005</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0.88260000000000005</v>
+      </c>
+      <c r="T4" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U4" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1</v>
       </c>
       <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="6">
         <v>4</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8">
+      <c r="F5" s="8">
         <v>201</v>
       </c>
-      <c r="E5" s="8">
+      <c r="G5" s="8">
         <v>300</v>
       </c>
-      <c r="F5" s="5">
+      <c r="H5" s="5">
         <v>1.1024449999999999</v>
       </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
@@ -851,10 +889,10 @@
         <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>0.90010000000000001</v>
+        <v>1</v>
       </c>
       <c r="N5" s="5">
-        <v>0.90010000000000001</v>
+        <v>1</v>
       </c>
       <c r="O5" s="5">
         <v>0.90010000000000001</v>
@@ -865,38 +903,44 @@
       <c r="Q5" s="5">
         <v>0.90010000000000001</v>
       </c>
-      <c r="R5" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S5" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R5" s="5">
+        <v>0.90010000000000001</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0.90010000000000001</v>
+      </c>
+      <c r="T5" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1</v>
       </c>
       <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="8">
+      <c r="F6" s="8">
         <v>301</v>
       </c>
-      <c r="E6" s="8">
+      <c r="G6" s="8">
         <v>400</v>
       </c>
-      <c r="F6" s="5">
+      <c r="H6" s="5">
         <v>1.1523350000000001</v>
       </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
@@ -910,10 +954,10 @@
         <v>1</v>
       </c>
       <c r="M6" s="5">
-        <v>0.91910000000000003</v>
+        <v>1</v>
       </c>
       <c r="N6" s="5">
-        <v>0.91910000000000003</v>
+        <v>1</v>
       </c>
       <c r="O6" s="5">
         <v>0.91910000000000003</v>
@@ -924,38 +968,44 @@
       <c r="Q6" s="5">
         <v>0.91910000000000003</v>
       </c>
-      <c r="R6" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R6" s="5">
+        <v>0.91910000000000003</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0.91910000000000003</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1</v>
       </c>
       <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8">
+      <c r="F7" s="8">
         <v>401</v>
       </c>
-      <c r="E7" s="8">
+      <c r="G7" s="8">
         <v>500</v>
       </c>
-      <c r="F7" s="5">
+      <c r="H7" s="5">
         <v>1.185543</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
       <c r="I7" s="5">
         <v>1</v>
       </c>
@@ -969,10 +1019,10 @@
         <v>1</v>
       </c>
       <c r="M7" s="5">
-        <v>0.93710000000000004</v>
+        <v>1</v>
       </c>
       <c r="N7" s="5">
-        <v>0.93710000000000004</v>
+        <v>1</v>
       </c>
       <c r="O7" s="5">
         <v>0.93710000000000004</v>
@@ -983,37 +1033,43 @@
       <c r="Q7" s="5">
         <v>0.93710000000000004</v>
       </c>
-      <c r="R7" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R7" s="5">
+        <v>0.93710000000000004</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0.93710000000000004</v>
+      </c>
+      <c r="T7" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1</v>
       </c>
       <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="6">
         <v>7</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8">
+      <c r="F8" s="8">
         <v>501</v>
       </c>
-      <c r="E8" s="8">
+      <c r="G8" s="8">
         <v>750</v>
       </c>
-      <c r="F8" s="5">
-        <v>1.28888</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
       <c r="H8" s="5">
-        <v>1</v>
+        <v>1.25888</v>
       </c>
       <c r="I8" s="5">
         <v>1</v>
@@ -1028,10 +1084,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="5">
-        <v>0.98250000000000004</v>
+        <v>1</v>
       </c>
       <c r="N8" s="5">
-        <v>0.98250000000000004</v>
+        <v>1</v>
       </c>
       <c r="O8" s="5">
         <v>0.98250000000000004</v>
@@ -1042,38 +1098,44 @@
       <c r="Q8" s="5">
         <v>0.98250000000000004</v>
       </c>
-      <c r="R8" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R8" s="5">
+        <v>0.98250000000000004</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0.98250000000000004</v>
+      </c>
+      <c r="T8" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1</v>
       </c>
       <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="6">
         <v>8</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8">
+      <c r="F9" s="8">
         <v>751</v>
       </c>
-      <c r="E9" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="G9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H9" s="5">
         <v>1.2878700000000001</v>
       </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1</v>
-      </c>
       <c r="I9" s="5">
         <v>1</v>
       </c>
@@ -1087,10 +1149,10 @@
         <v>1</v>
       </c>
       <c r="M9" s="5">
-        <v>1.0286999999999999</v>
+        <v>1</v>
       </c>
       <c r="N9" s="5">
-        <v>1.0286999999999999</v>
+        <v>1</v>
       </c>
       <c r="O9" s="5">
         <v>1.0286999999999999</v>
@@ -1101,38 +1163,44 @@
       <c r="Q9" s="5">
         <v>1.0286999999999999</v>
       </c>
-      <c r="R9" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R9" s="5">
+        <v>1.0286999999999999</v>
+      </c>
+      <c r="S9" s="5">
+        <v>1.0286999999999999</v>
+      </c>
+      <c r="T9" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1</v>
       </c>
       <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="6">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="8">
+      <c r="F10" s="8">
         <v>1001</v>
       </c>
-      <c r="E10" s="8">
+      <c r="G10" s="8">
         <v>1500</v>
       </c>
-      <c r="F10" s="5">
+      <c r="H10" s="5">
         <v>1.31</v>
       </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
       <c r="I10" s="5">
         <v>1</v>
       </c>
@@ -1146,10 +1214,10 @@
         <v>1</v>
       </c>
       <c r="M10" s="5">
-        <v>1.1183000000000001</v>
+        <v>1</v>
       </c>
       <c r="N10" s="5">
-        <v>1.1183000000000001</v>
+        <v>1</v>
       </c>
       <c r="O10" s="5">
         <v>1.1183000000000001</v>
@@ -1160,38 +1228,44 @@
       <c r="Q10" s="5">
         <v>1.1183000000000001</v>
       </c>
-      <c r="R10" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R10" s="5">
+        <v>1.1183000000000001</v>
+      </c>
+      <c r="S10" s="5">
+        <v>1.1183000000000001</v>
+      </c>
+      <c r="T10" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1</v>
       </c>
       <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="8">
+      <c r="F11" s="8">
         <v>1501</v>
       </c>
-      <c r="E11" s="8">
+      <c r="G11" s="8">
         <v>2000</v>
       </c>
-      <c r="F11" s="5">
+      <c r="H11" s="5">
         <v>1.355488</v>
       </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1</v>
-      </c>
       <c r="I11" s="5">
         <v>1</v>
       </c>
@@ -1205,10 +1279,10 @@
         <v>1</v>
       </c>
       <c r="M11" s="5">
-        <v>1.2103999999999999</v>
+        <v>1</v>
       </c>
       <c r="N11" s="5">
-        <v>1.2103999999999999</v>
+        <v>1</v>
       </c>
       <c r="O11" s="5">
         <v>1.2103999999999999</v>
@@ -1219,37 +1293,43 @@
       <c r="Q11" s="5">
         <v>1.2103999999999999</v>
       </c>
-      <c r="R11" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R11" s="5">
+        <v>1.2103999999999999</v>
+      </c>
+      <c r="S11" s="5">
+        <v>1.2103999999999999</v>
+      </c>
+      <c r="T11" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>1</v>
       </c>
       <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6">
         <v>11</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="8">
+      <c r="F12" s="8">
         <v>2001</v>
       </c>
-      <c r="E12" s="8">
+      <c r="G12" s="8">
         <v>2500</v>
       </c>
-      <c r="F12" s="5">
-        <v>1.3858775999999999</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
       <c r="H12" s="5">
-        <v>1</v>
+        <v>1.3758775999999999</v>
       </c>
       <c r="I12" s="5">
         <v>1</v>
@@ -1264,24 +1344,745 @@
         <v>1</v>
       </c>
       <c r="M12" s="5">
-        <v>1.3015000000000001</v>
+        <v>1</v>
       </c>
       <c r="N12" s="5">
-        <v>1.3015000000000001</v>
+        <v>1</v>
       </c>
       <c r="O12" s="5">
-        <v>1.3015000000000001</v>
+        <v>1.2515000000000001</v>
       </c>
       <c r="P12" s="5">
-        <v>1.3015000000000001</v>
+        <v>1.2515000000000001</v>
       </c>
       <c r="Q12" s="5">
-        <v>1.3015000000000001</v>
-      </c>
-      <c r="R12" s="6">
-        <v>1000</v>
-      </c>
-      <c r="S12" s="6">
+        <v>1.2515000000000001</v>
+      </c>
+      <c r="R12" s="5">
+        <v>1.2515000000000001</v>
+      </c>
+      <c r="S12" s="5">
+        <v>1.2515000000000001</v>
+      </c>
+      <c r="T12" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>1</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>50</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1.0138658599999999</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0.83809599999999995</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0.83809599999999995</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>0.83809599999999995</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0.83809599999999995</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0.83809599999999995</v>
+      </c>
+      <c r="T13" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>1</v>
+      </c>
+      <c r="B14" s="6">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="8">
+        <v>51</v>
+      </c>
+      <c r="G14" s="8">
+        <v>100</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1.0411029999999999</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0.84711199999999998</v>
+      </c>
+      <c r="P14" s="5">
+        <v>0.84711199999999998</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>0.84711199999999998</v>
+      </c>
+      <c r="R14" s="5">
+        <v>0.84711199999999998</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0.84711199999999998</v>
+      </c>
+      <c r="T14" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6">
+        <v>3</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="8">
+        <v>101</v>
+      </c>
+      <c r="G15" s="8">
+        <v>200</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1.0652482400000001</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0.86494800000000005</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0.86494800000000005</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>0.86494800000000005</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0.86494800000000005</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0.86494800000000005</v>
+      </c>
+      <c r="T15" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="8">
+        <v>201</v>
+      </c>
+      <c r="G16" s="8">
+        <v>300</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1.0803961</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0.88209800000000005</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0.88209800000000005</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>0.88209800000000005</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0.88209800000000005</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0.88209800000000005</v>
+      </c>
+      <c r="T16" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="6">
+        <v>5</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="8">
+        <v>301</v>
+      </c>
+      <c r="G17" s="8">
+        <v>400</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1.0947182500000001</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0.87314499999999995</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0.87314499999999995</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0.87314499999999995</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0.87314499999999995</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0.87314499999999995</v>
+      </c>
+      <c r="T17" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6">
+        <v>2</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="8">
+        <v>401</v>
+      </c>
+      <c r="G18" s="8">
+        <v>500</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1.12626585</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+      <c r="J18" s="5">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5">
+        <v>1</v>
+      </c>
+      <c r="M18" s="5">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0.89024499999999995</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0.89024499999999995</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>0.89024499999999995</v>
+      </c>
+      <c r="R18" s="5">
+        <v>0.89024499999999995</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0.89024499999999995</v>
+      </c>
+      <c r="T18" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>7</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="8">
+        <v>501</v>
+      </c>
+      <c r="G19" s="8">
+        <v>750</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1.1204031999999999</v>
+      </c>
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5">
+        <v>1</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0.87442500000000001</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0.87442500000000001</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0.87442500000000001</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0.87442500000000001</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0.87442500000000001</v>
+      </c>
+      <c r="T19" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>1</v>
+      </c>
+      <c r="B20" s="6">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="8">
+        <v>751</v>
+      </c>
+      <c r="G20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1.1590830000000001</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1</v>
+      </c>
+      <c r="M20" s="5">
+        <v>1</v>
+      </c>
+      <c r="N20" s="5">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0.92582999999999993</v>
+      </c>
+      <c r="P20" s="5">
+        <v>0.92582999999999993</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0.92582999999999993</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0.92582999999999993</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0.92582999999999993</v>
+      </c>
+      <c r="T20" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="6">
+        <v>9</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1001</v>
+      </c>
+      <c r="G21" s="8">
+        <v>1500</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1.179</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5">
+        <v>1</v>
+      </c>
+      <c r="M21" s="5">
+        <v>1</v>
+      </c>
+      <c r="N21" s="5">
+        <v>1</v>
+      </c>
+      <c r="O21" s="5">
+        <v>1.0064700000000002</v>
+      </c>
+      <c r="P21" s="5">
+        <v>1.0064700000000002</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>1.0064700000000002</v>
+      </c>
+      <c r="R21" s="5">
+        <v>1.0064700000000002</v>
+      </c>
+      <c r="S21" s="5">
+        <v>1.0064700000000002</v>
+      </c>
+      <c r="T21" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>1</v>
+      </c>
+      <c r="B22" s="6">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="6">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1501</v>
+      </c>
+      <c r="G22" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="5">
+        <v>1.20638432</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5">
+        <v>1</v>
+      </c>
+      <c r="M22" s="5">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5">
+        <v>1.077256</v>
+      </c>
+      <c r="P22" s="5">
+        <v>1.077256</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>1.077256</v>
+      </c>
+      <c r="R22" s="5">
+        <v>1.077256</v>
+      </c>
+      <c r="S22" s="5">
+        <v>1.077256</v>
+      </c>
+      <c r="T22" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>1</v>
+      </c>
+      <c r="B23" s="6">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6">
+        <v>11</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2001</v>
+      </c>
+      <c r="G23" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1.224531064</v>
+      </c>
+      <c r="I23" s="5">
+        <v>1</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <v>1</v>
+      </c>
+      <c r="M23" s="5">
+        <v>1</v>
+      </c>
+      <c r="N23" s="5">
+        <v>1</v>
+      </c>
+      <c r="O23" s="5">
+        <v>1.1138350000000001</v>
+      </c>
+      <c r="P23" s="5">
+        <v>1.1138350000000001</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>1.1138350000000001</v>
+      </c>
+      <c r="R23" s="5">
+        <v>1.1138350000000001</v>
+      </c>
+      <c r="S23" s="5">
+        <v>1.1138350000000001</v>
+      </c>
+      <c r="T23" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U23" s="6">
         <v>1</v>
       </c>
     </row>
